--- a/Blood-results-redacted-gemma3.xlsx
+++ b/Blood-results-redacted-gemma3.xlsx
@@ -91,7 +91,7 @@
     <t>Only one illegal substance, Tetrahydrocannabinol (THC), was detected. The concentration was 28 UG/L, which may be relevant for impairment charges, but no alcohol or other illegal drugs were detected.</t>
   </si>
   <si>
-    <t>The context doesn’t explicitly state who requested the blood analysis. It only states that the analysis was conducted “From” the Forensic Science Laboratory.</t>
+    <t>The context doesn’t state who requested the blood analysis. It simply indicates that the analysis was performed by the Forensic Science Laboratory.</t>
   </si>
   <si>
     <t>The subject of the analysis was a driver whose blood sample was being analyzed.</t>
@@ -100,45 +100,38 @@
     <t>Blood sample</t>
   </si>
   <si>
-    <t>The reason for the test was not explicitly stated in the document. However, the document indicates it was a “MAJOR CRASH INVESTIGATION”.</t>
-  </si>
-  <si>
-    <t>The analyst within the Chemistry Centre (WA), Perth performed the test.</t>
-  </si>
-  <si>
-    <t>Based on the provided context, here are the charges that could be preferred against a driver:
-*   **Section 64AC Road Traffic Act 1974:** Driving with a prescribed illicit drug present in a person’s oral fluid or blood (This is the easiest charge to prove).
-*   **Section 64AB Road Traffic Act 1974:** Driving while impaired by drugs (This is applicable if Section 64AC isn't sufficient).
-*   **Section 63 Road Traffic Act 1974:** Driving under the influence of drugs (This charge requires supporting evidence, such as visual observation).</t>
-  </si>
-  <si>
-    <t>Here’s a list of the substances found during the analysis and their concentrations, based on the provided text:
+    <t>According to the document, the reason for the test was “Probation: No”.</t>
+  </si>
+  <si>
+    <t>The analyst from the Chemistry Centre (WA) performed the test.</t>
+  </si>
+  <si>
+    <t>Based on the provided document, the following charges are possible:
+*   **Section 64AC Road Traffic Act 1974:** Driving with a prescribed illicit drug present in a person's oral fluid or blood (This is the easiest charge to prove).
+*   **Section 64AB Road Traffic Act 1974:** Driving while impaired by drugs (Applicable in some cases).
+*   **Section 63 Road Traffic Act 1974:** Driving under the influence of drugs (Requires supporting evidence, such as visual observation of the apprehending officer or independent witnesses).</t>
+  </si>
+  <si>
+    <t>Here’s a list of the substances detected and their concentrations, based on the provided document:
 *   **Alcohol:** Not Detected
 *   **Gamma Hydroxybutyric Acid (GHB):** Not Detected
 *   **Tetrahydrocannabinol (THC):** Not Detected
 *   **Common Basic Drugs:** Not Detected</t>
   </si>
   <si>
-    <t>Based on the provided context, a blood sample was analyzed for the presence of drugs. This is likely done to determine if a driver was impaired due to drug use, which would be relevant for potential charges under the Road Traffic Act.</t>
-  </si>
-  <si>
-    <t>Based on the provided text, a Pharmacological Opinion Report is recommended if you believe you have sufficient evidence to support a charge of driving whilst impaired or DUI drug/alcohol. The report will detail the effects of drugs and offer an expert opinion on whether the driver was impaired. 
-To obtain this report, you’ll need to provide as much information as possible, including:
-*   Chem Centre analysis results (blood and urine)
-*   Form 4 (Assessment of driver conduct, condition, and appearance)
-*   Statements from apprehending officers and witnesses
-*   Sobriety and Breath Papers
-*   Accident reports and IMS reports.
-The report costs a minimum of $3,000 inclusive of GST and is typically borne by Breath and Operations. Photocopies should be attached where possible.</t>
-  </si>
-  <si>
-    <t>Based on the provided document, the following substances were found during the analysis:
-*   **Alcohol:** Detected at 0.000 grams of alcohol per 100 mL of blood.
+    <t>Based on the provided context, a blood sample was analyzed for the presence of drugs. The analysis was performed to determine if drugs were present in the blood, which is relevant to potential charges under the Road Traffic Act, 1974.</t>
+  </si>
+  <si>
+    <t>The report, provided by a pharmacologist, will detail the effects of drugs on the driver and offer an expert opinion on whether impairment or influence (alcohol and drugs) was present. To obtain this report, you must provide as much information as possible, including: Chem Centre analysis results, Form 4 assessment, officer statements, witness statements, sobriety test papers, breath papers, accident reports, IMS running sheets, and the Investigative Action Register. The report costs a minimum of $3,000 inclusive of GST, and is typically borne by Breath and Operations. Photocopies should be attached whenever possible.</t>
+  </si>
+  <si>
+    <t>Here’s the breakdown of the analysis results and the answer to your query:
+**Legal Substances Found:**
+*   **Alcohol:** Detected (0.000 grams of alcohol per 100 mL of blood)
 *   **Gamma Hydroxybutyric Acid (GHB)**
-*   **Tetrahydrocannabinol (THC)**
-*   **Common Basic Drugs**
+*   **Tetrahydrocannabinol (THC - Common Basic Drugs)**
 **Were there any substances present that were above the allowed limit?**
-Yes, the sample contained 0.000 grams of alcohol per 100 mL of blood. The document doesn't state what the allowed limit is.</t>
+*   Yes, there was alcohol present. The report states 0.000 grams of alcohol per 100 mL of blood. This is above the legal limit for driving under the influence in Western Australia.</t>
   </si>
 </sst>
 </file>
